--- a/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
+++ b/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
@@ -7,16 +7,56 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="未匹配_工号" sheetId="1" r:id="rId1"/>
-    <sheet name="未匹配_供应商" sheetId="2" r:id="rId2"/>
-    <sheet name="未匹配_费用科目" sheetId="3" r:id="rId3"/>
+    <sheet name="必输字段未达100%" sheetId="1" r:id="rId1"/>
+    <sheet name="未匹配_工号" sheetId="2" r:id="rId2"/>
+    <sheet name="未匹配_供应商" sheetId="3" r:id="rId3"/>
+    <sheet name="未匹配_费用科目" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+  <si>
+    <t>必输字段</t>
+  </si>
+  <si>
+    <t>填充数</t>
+  </si>
+  <si>
+    <t>缺失数</t>
+  </si>
+  <si>
+    <t>总数</t>
+  </si>
+  <si>
+    <t>填充率</t>
+  </si>
+  <si>
+    <t>申请人工号</t>
+  </si>
+  <si>
+    <t>订单编号</t>
+  </si>
+  <si>
+    <t>收款方编码</t>
+  </si>
+  <si>
+    <t>费用项目编码</t>
+  </si>
+  <si>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>97.2%</t>
+  </si>
+  <si>
+    <t>94.8%</t>
+  </si>
   <si>
     <t>未匹配_填单人(工号)</t>
   </si>
@@ -434,17 +474,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>1086</v>
+      </c>
+      <c r="C2">
         <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1087</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1087</v>
+      </c>
+      <c r="D3">
+        <v>1087</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>1057</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>1087</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1030</v>
+      </c>
+      <c r="C5">
+        <v>57</v>
+      </c>
+      <c r="D5">
+        <v>1087</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -454,122 +569,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -579,27 +589,152 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
+++ b/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
@@ -8,16 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="必输字段未达100%" sheetId="1" r:id="rId1"/>
-    <sheet name="未匹配_工号" sheetId="2" r:id="rId2"/>
-    <sheet name="未匹配_供应商" sheetId="3" r:id="rId3"/>
-    <sheet name="未匹配_费用科目" sheetId="4" r:id="rId4"/>
+    <sheet name="缺失_申请人工号" sheetId="2" r:id="rId2"/>
+    <sheet name="缺失_收款方编码" sheetId="3" r:id="rId3"/>
+    <sheet name="缺失_费用项目编码" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="106">
   <si>
     <t>必输字段</t>
   </si>
@@ -58,91 +58,283 @@
     <t>94.8%</t>
   </si>
   <si>
-    <t>未匹配_填单人(工号)</t>
+    <t>来源单据编号</t>
+  </si>
+  <si>
+    <t>泛微原表-填单人</t>
+  </si>
+  <si>
+    <t>Y1-V-386-0001</t>
   </si>
   <si>
     <t>罗文静</t>
   </si>
   <si>
-    <t>未匹配_付款对象(收款方编码)</t>
+    <t>泛微原表-付款对象</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-123-0014</t>
+  </si>
+  <si>
+    <t>Y1-A1-2026-020-0022</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-123-0013</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-153-0004</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-166-0007</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-123-0009</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-166-0006</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-112-0001</t>
+  </si>
+  <si>
+    <t>Y1-Y2-2026-003-0052</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-123-0008</t>
+  </si>
+  <si>
+    <t>Y1-A1-2026-013-0001</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-140-0018</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-166-0005</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-123-0007</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-065-0008</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-017-0008</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-166-0004</t>
+  </si>
+  <si>
+    <t>Y1-A1-2026-014-0010</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-140-0014</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-140-0013</t>
+  </si>
+  <si>
+    <t>Y1-B2-2026-140-0012</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-022-0014</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-022-0013</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-022-0005</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-022-0004</t>
+  </si>
+  <si>
+    <t>Y1-Y2-2026-003-0011</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-022-0002</t>
+  </si>
+  <si>
+    <t>Y1-V-011-0015</t>
+  </si>
+  <si>
+    <t>Y1-A4-2026-026-0001</t>
+  </si>
+  <si>
+    <t>Y1-A2-2025-027-0045</t>
+  </si>
+  <si>
+    <t>信德前滩(上海)文化发展有限公司前滩雅辰酒店分公司</t>
+  </si>
+  <si>
+    <t>天津博泰天宇科技发展有限公司</t>
+  </si>
+  <si>
+    <t>上海安保消防技术有限公司</t>
+  </si>
+  <si>
+    <t>武汉乐顿酒店管理有限公司</t>
+  </si>
+  <si>
+    <t>广东云杰机电设备工程有限公司</t>
+  </si>
+  <si>
+    <t>上海林溪酒店管理有限公司</t>
+  </si>
+  <si>
+    <t>贵州陌客视觉科技有限公司</t>
+  </si>
+  <si>
+    <t>杭州滨江奥体运营有限公司</t>
+  </si>
+  <si>
+    <t>深圳市变色宝工艺制品有限公司</t>
+  </si>
+  <si>
+    <t>广州风之羽仿生科技有限公司</t>
+  </si>
+  <si>
+    <t>上海甲第园筑景观工程有限公司</t>
+  </si>
+  <si>
+    <t>浙江毅正保安服务有限公司</t>
+  </si>
+  <si>
+    <t>北京阿狸火文化传媒有限公司</t>
   </si>
   <si>
     <t>上海京辰消防工程有限公司</t>
   </si>
   <si>
-    <t>上海安保消防技术有限公司</t>
-  </si>
-  <si>
-    <t>上海林溪酒店管理有限公司</t>
-  </si>
-  <si>
-    <t>上海甲第园筑景观工程有限公司</t>
+    <t>首都医科大学附属北京康复医院</t>
   </si>
   <si>
     <t>上海确佳贸易有限公司</t>
   </si>
   <si>
+    <t>嘉兴市南湖区保安服务有限公司</t>
+  </si>
+  <si>
+    <t>广州雅渲纺织品有限公司</t>
+  </si>
+  <si>
+    <t>太仓市人民法院诉讼费专户</t>
+  </si>
+  <si>
+    <t>东莞安信玩具有限公司</t>
+  </si>
+  <si>
+    <t>安付宝支付有限公司客户备付金</t>
+  </si>
+  <si>
     <t>上海自如企业管理有限公司</t>
   </si>
   <si>
-    <t>东莞安信玩具有限公司</t>
-  </si>
-  <si>
-    <t>信德前滩(上海)文化发展有限公司前滩雅辰酒店分公司</t>
-  </si>
-  <si>
-    <t>北京阿狸火文化传媒有限公司</t>
-  </si>
-  <si>
-    <t>嘉兴市南湖区保安服务有限公司</t>
-  </si>
-  <si>
-    <t>天津博泰天宇科技发展有限公司</t>
-  </si>
-  <si>
-    <t>太仓市人民法院诉讼费专户</t>
-  </si>
-  <si>
-    <t>安付宝支付有限公司客户备付金</t>
-  </si>
-  <si>
-    <t>广东云杰机电设备工程有限公司</t>
-  </si>
-  <si>
-    <t>广州雅渲纺织品有限公司</t>
-  </si>
-  <si>
-    <t>广州风之羽仿生科技有限公司</t>
-  </si>
-  <si>
-    <t>杭州滨江奥体运营有限公司</t>
-  </si>
-  <si>
-    <t>武汉乐顿酒店管理有限公司</t>
-  </si>
-  <si>
-    <t>浙江毅正保安服务有限公司</t>
-  </si>
-  <si>
-    <t>深圳市变色宝工艺制品有限公司</t>
-  </si>
-  <si>
-    <t>贵州陌客视觉科技有限公司</t>
-  </si>
-  <si>
-    <t>首都医科大学附属北京康复医院</t>
-  </si>
-  <si>
-    <t>未匹配_预算科目(费用项目)</t>
+    <t>泛微原表-预算科目</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0021</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-021-0012</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-038-0004</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-040-0011</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0019</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-011-0023</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0016</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-021-0011</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-023-0003</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-038-0003</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-021-0010</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-040-0010</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-011-0021</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0013</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0011</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-038-0002</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-007-0001</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-021-0007</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-040-0008</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-011-0015</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0009</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0007</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-038-0001</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-040-0004</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-011-0011</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-040-0001</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-004-0002</t>
+  </si>
+  <si>
+    <t>Y1-A2-2025-013-0013</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-021-0003</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-021-0002</t>
+  </si>
+  <si>
+    <t>Y1-A2-2026-023-0001</t>
+  </si>
+  <si>
+    <t>Y1-A2-2025-010-0030</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR632能耗费/AR6321办公房屋</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR633水费/AR6331办公房屋</t>
   </si>
   <si>
     <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR631电费/AR6311办公房屋</t>
-  </si>
-  <si>
-    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR632能耗费/AR6321办公房屋</t>
-  </si>
-  <si>
-    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR633水费/AR6331办公房屋</t>
   </si>
 </sst>
 </file>
@@ -569,17 +761,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -589,122 +787,255 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -714,27 +1045,471 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>102</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
+++ b/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
@@ -7,17 +7,17 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="必输字段未达100%" sheetId="1" r:id="rId1"/>
-    <sheet name="缺失_申请人工号" sheetId="2" r:id="rId2"/>
-    <sheet name="缺失_收款方编码" sheetId="3" r:id="rId3"/>
-    <sheet name="缺失_费用项目编码" sheetId="4" r:id="rId4"/>
+    <sheet name="供应商_必输字段未达100%" sheetId="1" r:id="rId1"/>
+    <sheet name="供应商_缺失_收款方编码" sheetId="2" r:id="rId2"/>
+    <sheet name="供应商_缺失_费用项目编码" sheetId="3" r:id="rId3"/>
+    <sheet name="灵工_必输字段未达100%" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="101">
   <si>
     <t>必输字段</t>
   </si>
@@ -34,9 +34,6 @@
     <t>填充率</t>
   </si>
   <si>
-    <t>申请人工号</t>
-  </si>
-  <si>
     <t>订单编号</t>
   </si>
   <si>
@@ -46,9 +43,6 @@
     <t>费用项目编码</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
     <t>0.0%</t>
   </si>
   <si>
@@ -59,15 +53,6 @@
   </si>
   <si>
     <t>来源单据编号</t>
-  </si>
-  <si>
-    <t>泛微原表-填单人</t>
-  </si>
-  <si>
-    <t>Y1-V-386-0001</t>
-  </si>
-  <si>
-    <t>罗文静</t>
   </si>
   <si>
     <t>泛微原表-付款对象</t>
@@ -666,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -691,16 +676,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1086</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1087</v>
       </c>
       <c r="D2">
         <v>1087</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -708,16 +693,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1057</v>
       </c>
       <c r="C3">
-        <v>1087</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>1087</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -725,33 +710,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1057</v>
+        <v>1030</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D4">
         <v>1087</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1030</v>
-      </c>
-      <c r="C5">
-        <v>57</v>
-      </c>
-      <c r="D5">
-        <v>1087</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -761,23 +729,255 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -787,255 +987,471 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1045,471 +1461,75 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>2731</v>
+      </c>
+      <c r="D2">
+        <v>2731</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>2731</v>
+      </c>
+      <c r="D3">
+        <v>2731</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>86</v>
-      </c>
-      <c r="B32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B43" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>97</v>
-      </c>
-      <c r="B47" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>101</v>
-      </c>
-      <c r="B54" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>101</v>
-      </c>
-      <c r="B55" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>102</v>
-      </c>
-      <c r="B56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>102</v>
-      </c>
-      <c r="B58" t="s">
-        <v>103</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>2731</v>
+      </c>
+      <c r="D4">
+        <v>2731</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
+++ b/output/ap_prepayment_opening/未匹配清单_预付期初_20260614.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="101">
   <si>
     <t>必输字段</t>
   </si>
@@ -1461,7 +1461,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1515,23 +1515,6 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>2731</v>
-      </c>
-      <c r="D4">
-        <v>2731</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
